--- a/StructureDefinition-SEEHDSLMAccessLog.xlsx
+++ b/StructureDefinition-SEEHDSLMAccessLog.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMAccessLog.xlsx
+++ b/StructureDefinition-SEEHDSLMAccessLog.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMAccessLog.xlsx
+++ b/StructureDefinition-SEEHDSLMAccessLog.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMAccessLog.xlsx
+++ b/StructureDefinition-SEEHDSLMAccessLog.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1235" uniqueCount="179">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:49:57+00:00</t>
+    <t>2026-10-09T07:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,95 +247,322 @@
     <t>Base</t>
   </si>
   <si>
-    <t>SEEHDSLMAccessLog.accessLogId</t>
+    <t>SEEHDSLMAccessLog.accessLogsResult</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier
+    <t xml:space="preserve">BackboneElement
 </t>
   </si>
   <si>
-    <t>Loggpostens identifierare</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAccessLog.patientId</t>
-  </si>
-  <si>
-    <t>Patientidentifierare</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAccessLog.accessTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
+    <t>Resultatobjekt med status huruvida tjänsten returnerar ok eller om fel uppstått</t>
+  </si>
+  <si>
+    <t>Resultatobjekt med status huruvida tjänsten returnerar ok eller om fel uppstått. Om tjänsten utförts korrekt returneras en lista med patientinformation och resultatkod OK. Vid eventuella fel i tjänsteanropet returneras ingen patientinformation. Statuskod som beskriver orsaken till fel returneras då tillsammans med ett felmeddelande.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
-    <t>Åtkomsttidpunkt (UTC)</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAccessLog.accessType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Åtkomsttyp (Läsning/Sökning)</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAccessLog.accessSubType</t>
-  </si>
-  <si>
-    <t>Åtkomstundertyp</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAccessLog.accessOutcome</t>
-  </si>
-  <si>
-    <t>Utfall (Beviljad/Nekad)</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAccessLog.accessPurpose</t>
-  </si>
-  <si>
-    <t>Åtkomstsyfte (Vård/Administration)</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAccessLog.userId</t>
-  </si>
-  <si>
-    <t>Användarens HSA-id</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAccessLog.userRole</t>
-  </si>
-  <si>
-    <t>Användarroll</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAccessLog.userOrganization</t>
-  </si>
-  <si>
-    <t>Användarens organisations HSA-id</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAccessLog.sourceSystemHSAId</t>
+    <t>SEEHDSLMAccessLog.accessLogsResult.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Källsystem (loggkälla)</t>
-  </si>
-  <si>
-    <t>SEEHDSLMAccessLog.accessedResource</t>
-  </si>
-  <si>
-    <t>Resurs/tjänst som åtkoms</t>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.reportResult</t>
+  </si>
+  <si>
+    <t>reportResult</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.reportResult.id</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.reportResult.extension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.reportResult.modifierExtension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.reportResult.result</t>
+  </si>
+  <si>
+    <t>Datatyp som returneras som ett generellt svar från alla förändrande tjänster, t.ex.</t>
+  </si>
+  <si>
+    <t>Datatyp som returneras som ett generellt svar från alla förändrande tjänster, t.ex. skapa, radera, etc. En anropande klient skall alltid kontrollera att resultatkoden inte innehåller fel för att på så sätt veta om anropet lyckades. Alla svarskoder förutom OK och INFO betyder att åtgärden inte genomfördes.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.reportResult.result.id</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.reportResult.result.extension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.reportResult.result.modifierExtension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.reportResult.result.resultCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivString
+</t>
+  </si>
+  <si>
+    <t>resultCode</t>
+  </si>
+  <si>
+    <t>Tillåtna värden enligt XSD: OK, INFO, ERROR, VALIDATION_ERROR, ACCESSDENIED, REPORT_ON_QUEUE, REPORT_IN_PROCESS, REPORT_NOT_FOUND, MAX_QUERY_RESULT_EXCEEDED.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.reportResult.result.resultText</t>
+  </si>
+  <si>
+    <t>resultText</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.reportResult.startInterval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivDateTime
+</t>
+  </si>
+  <si>
+    <t>Parameter som anger datum för första loggposten som finns för uppföljning när rapporten skapas</t>
+  </si>
+  <si>
+    <t>Parameter som anger datum för första loggposten som finns för uppföljning när rapporten skapas.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.reportResult.endInterval</t>
+  </si>
+  <si>
+    <t>Parameter som anger datum för sista loggposten som finns för uppföljning när rapporten skapas</t>
+  </si>
+  <si>
+    <t>Parameter som anger datum för sista loggposten som finns för uppföljning när rapporten skapas.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.reportResult.queuedReportId</t>
+  </si>
+  <si>
+    <t>Parameter som anger id på den rapport som efterfrågas och returneras om anropet avslutas innan rapporten är …</t>
+  </si>
+  <si>
+    <t>Parameter som anger id på den rapport som efterfrågas och returneras om anropet avslutas innan rapporten är genererad. Ytterligare anrop kan då göras med rapport id som inparameter för att hämta rapport. Finns för att undvika hängande anrop samt köa upp jobb vid hög belastning.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.reportResult.queueTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivInteger
+</t>
+  </si>
+  <si>
+    <t>Anger förväntad tid i sekunder tills en köad rapport (identifierad med queuedReportId) kan levereras av …</t>
+  </si>
+  <si>
+    <t>Anger förväntad tid i sekunder tills en köad rapport (identifierad med queuedReportId) kan levereras av producenten.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.accesssLogs</t>
+  </si>
+  <si>
+    <t>Datatyp som håller lista med Access loggar</t>
+  </si>
+  <si>
+    <t>Datatyp som håller lista med Access loggar. Kan vara en tom lista.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.accesssLogs.id</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.accesssLogs.extension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.accesssLogs.modifierExtension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.accesssLogs.accessLog</t>
+  </si>
+  <si>
+    <t>Datatyp som håller information för vilken vårdgivare och vårdenhet som haft åtkomst samt typ av resurs, orsak …</t>
+  </si>
+  <si>
+    <t>Datatyp som håller information för vilken vårdgivare och vårdenhet som haft åtkomst samt typ av resurs, orsak och tidpunkt.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.accesssLogs.accessLog.id</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.accesssLogs.accessLog.extension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.accesssLogs.accessLog.modifierExtension</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.accesssLogs.accessLog.careProviderId</t>
+  </si>
+  <si>
+    <t>Vårdgivare som haft åtkomst</t>
+  </si>
+  <si>
+    <t>Vårdgivare som haft åtkomst.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.accesssLogs.accessLog.careProviderName</t>
+  </si>
+  <si>
+    <t>Namn på vårdgivare som haft åtkomst</t>
+  </si>
+  <si>
+    <t>Namn på vårdgivare som haft åtkomst.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.accesssLogs.accessLog.careUnitId</t>
+  </si>
+  <si>
+    <t>Vårdenhet som haft åtkomst</t>
+  </si>
+  <si>
+    <t>Vårdenhet som haft åtkomst.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.accesssLogs.accessLog.careUnitName</t>
+  </si>
+  <si>
+    <t>Namn på vårdenhet som haft åtkomst</t>
+  </si>
+  <si>
+    <t>Namn på vårdenhet som haft åtkomst.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.accesssLogs.accessLog.accessDate</t>
+  </si>
+  <si>
+    <t>Tidpunkt för åtkomst</t>
+  </si>
+  <si>
+    <t>Tidpunkt för åtkomst.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.accesssLogs.accessLog.userId</t>
+  </si>
+  <si>
+    <t>Vårdaktörens id</t>
+  </si>
+  <si>
+    <t>Vårdaktörens id.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.accesssLogs.accessLog.userName</t>
+  </si>
+  <si>
+    <t>Namn på vårdaktör</t>
+  </si>
+  <si>
+    <t>Namn på vårdaktör.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.accesssLogs.accessLog.userTitle</t>
+  </si>
+  <si>
+    <t>Titel på vårdaktör</t>
+  </si>
+  <si>
+    <t>Titel på vårdaktör.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.accesssLogs.accessLog.purpose</t>
+  </si>
+  <si>
+    <t>Information om syftet med aktiviten</t>
+  </si>
+  <si>
+    <t>Information om syftet med aktiviten. kan vara något av dessa värden: Vård och behandling, Kvalitetssäkring, Annan dokumentation enligt lag, Statistik, Administration och Kvalitetsregister.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMAccessLog.accessLogsResult.accesssLogs.accessLog.resourceType</t>
+  </si>
+  <si>
+    <t>Typ av resurs</t>
+  </si>
+  <si>
+    <t>Typ av resurs. Se ref #7 och #8</t>
   </si>
 </sst>
 </file>
@@ -637,24 +864,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ14"/>
+  <dimension ref="A1:AJ38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="34.07421875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="34.07421875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="66.1328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="66.1328125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="14.78515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="56.82421875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -668,10 +895,10 @@
     <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.07421875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="66.1328125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -921,7 +1148,7 @@
         <v>80</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -984,15 +1211,15 @@
         <v>72</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1000,7 +1227,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>78</v>
@@ -1015,13 +1242,13 @@
         <v>72</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1072,10 +1299,10 @@
         <v>72</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH4" t="s" s="2">
         <v>78</v>
@@ -1089,21 +1316,21 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>72</v>
@@ -1115,15 +1342,17 @@
         <v>72</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N5" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N5" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>72</v>
@@ -1160,71 +1389,75 @@
         <v>72</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD5" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N6" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O6" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P6" t="s" s="2">
         <v>72</v>
       </c>
@@ -1272,27 +1505,27 @@
         <v>72</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1300,7 +1533,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>78</v>
@@ -1315,13 +1548,13 @@
         <v>72</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1372,10 +1605,10 @@
         <v>72</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
         <v>78</v>
@@ -1384,15 +1617,15 @@
         <v>72</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1400,7 +1633,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G8" t="s" s="2">
         <v>78</v>
@@ -1415,13 +1648,13 @@
         <v>72</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1472,10 +1705,10 @@
         <v>72</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH8" t="s" s="2">
         <v>78</v>
@@ -1489,21 +1722,21 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>72</v>
@@ -1515,15 +1748,17 @@
         <v>72</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>72</v>
@@ -1560,71 +1795,75 @@
         <v>72</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O10" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P10" t="s" s="2">
         <v>72</v>
       </c>
@@ -1672,27 +1911,27 @@
         <v>72</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1700,7 +1939,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>78</v>
@@ -1715,13 +1954,13 @@
         <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1772,10 +2011,10 @@
         <v>72</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AH11" t="s" s="2">
         <v>78</v>
@@ -1784,15 +2023,15 @@
         <v>72</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1815,13 +2054,13 @@
         <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1872,7 +2111,7 @@
         <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>73</v>
@@ -1889,21 +2128,21 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>72</v>
@@ -1915,15 +2154,17 @@
         <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>72</v>
@@ -1960,71 +2201,75 @@
         <v>72</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="L14" t="s" s="2">
-        <v>105</v>
-      </c>
       <c r="M14" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O14" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>72</v>
       </c>
@@ -2072,18 +2317,2430 @@
         <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q15" s="2"/>
+      <c r="R15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q18" s="2"/>
+      <c r="R18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O23" s="2"/>
+      <c r="P23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q23" s="2"/>
+      <c r="R23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O24" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="AG14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
+      <c r="P24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="P28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/StructureDefinition-SEEHDSLMAccessLog.xlsx
+++ b/StructureDefinition-SEEHDSLMAccessLog.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMAccessLog.xlsx
+++ b/StructureDefinition-SEEHDSLMAccessLog.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMAccessLog.xlsx
+++ b/StructureDefinition-SEEHDSLMAccessLog.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMAccessLog.xlsx
+++ b/StructureDefinition-SEEHDSLMAccessLog.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMAccessLog.xlsx
+++ b/StructureDefinition-SEEHDSLMAccessLog.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
